--- a/backtest_runs/20260410_193731/by_symbol/ICCI/ICCI.xlsx
+++ b/backtest_runs/20260410_193731/by_symbol/ICCI/ICCI.xlsx
@@ -465,12 +465,12 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>same_side_as_oracle</t>
+          <t>same_side_as_actual</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_diff_oracle_minus_model</t>
+          <t>daily_pnl_diff_actual_minus_model</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -480,7 +480,7 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>suggestion_oracle</t>
+          <t>suggestion_actual</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -490,7 +490,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_oracle</t>
+          <t>daily_pnl_actual</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>equity_oracle</t>
+          <t>equity_actual</t>
         </is>
       </c>
     </row>
@@ -538,10 +538,10 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>100000</v>
@@ -633,7 +633,7 @@
         <v>-2668.800000000002</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K4" s="3" t="n">
         <v>98915.8</v>
@@ -725,7 +725,7 @@
         <v>-667.2000000000006</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K6" s="3" t="n">
         <v>98248.60000000001</v>
@@ -768,10 +768,10 @@
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K7" s="2" t="n">
         <v>98248.60000000001</v>
@@ -860,10 +860,10 @@
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K9" s="2" t="n">
         <v>106588.6</v>
@@ -909,7 +909,7 @@
         <v>-1417.799999999999</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K10" s="3" t="n">
         <v>105170.8</v>
@@ -1093,7 +1093,7 @@
         <v>-4086.600000000002</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K14" s="3" t="n">
         <v>118514.8</v>
@@ -1139,7 +1139,7 @@
         <v>-833.999999999997</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K15" s="3" t="n">
         <v>117680.8</v>
@@ -1231,7 +1231,7 @@
         <v>-2918.999999999997</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K17" s="3" t="n">
         <v>118514.8</v>
@@ -1277,7 +1277,7 @@
         <v>-8006.400000000007</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K18" s="3" t="n">
         <v>110508.4</v>
@@ -1461,7 +1461,7 @@
         <v>-5587.799999999999</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K22" s="3" t="n">
         <v>116846.8</v>
@@ -1553,7 +1553,7 @@
         <v>-2085</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K24" s="3" t="n">
         <v>120683.2</v>
@@ -1645,7 +1645,7 @@
         <v>-1000.800000000008</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K26" s="3" t="n">
         <v>125103.4</v>
